--- a/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="430">
   <si>
     <t>sheet</t>
   </si>
@@ -806,16 +806,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>021f6f1989b638082df99df6839be132</t>
+    <t>03_Group_comparisons/Muscle_strength/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>4a470e09e1f60a5ee5de48beaf281dce</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>c3c35e87f9ae9f6a9412d96f8c8a33bf</t>
@@ -830,22 +830,22 @@
     <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/clustering.xlsx</t>
-  </si>
-  <si>
-    <t>810ad67589d07d350257d7bfb5834a74</t>
+    <t>02_Groups/Muscle_strength/c_data/clustering.xlsx</t>
+  </si>
+  <si>
+    <t>c01dbfe8f31b666a734c29c8bacbd341</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/02_Design_Contrasts/c_data/design.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/01_Design_Contrasts/c_data/design.rds</t>
   </si>
   <si>
     <t>c0cfb05785ba25feadb966caf1fa5a50</t>
@@ -956,12 +956,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -1034,6 +1046,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -1046,6 +1070,15 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -1055,9 +1088,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1094,6 +1124,9 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1172,6 +1205,12 @@
     <t>1.3.0</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -1269,6 +1308,12 @@
   </si>
   <si>
     <t>xml2</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -1796,7 +1841,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2071,15 +2116,15 @@
         <v>323</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" t="s">
         <v>325</v>
-      </c>
-      <c r="B26" t="s">
-        <v>315</v>
       </c>
       <c r="C26" t="s">
         <v>280</v>
@@ -2093,15 +2138,15 @@
         <v>327</v>
       </c>
       <c r="C27" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C28" t="s">
         <v>280</v>
@@ -2148,7 +2193,7 @@
         <v>337</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2203,7 +2248,7 @@
         <v>347</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2211,7 +2256,7 @@
         <v>348</v>
       </c>
       <c r="B38" t="s">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="C38" t="s">
         <v>280</v>
@@ -2219,10 +2264,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>349</v>
+      </c>
+      <c r="B39" t="s">
         <v>350</v>
-      </c>
-      <c r="B39" t="s">
-        <v>351</v>
       </c>
       <c r="C39" t="s">
         <v>280</v>
@@ -2230,10 +2275,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>351</v>
+      </c>
+      <c r="B40" t="s">
         <v>352</v>
-      </c>
-      <c r="B40" t="s">
-        <v>353</v>
       </c>
       <c r="C40" t="s">
         <v>280</v>
@@ -2241,10 +2286,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="C41" t="s">
         <v>280</v>
@@ -2252,32 +2297,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C42" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C44" t="s">
         <v>280</v>
@@ -2285,10 +2330,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C45" t="s">
         <v>280</v>
@@ -2296,10 +2341,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" t="s">
         <v>280</v>
@@ -2307,10 +2352,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
         <v>280</v>
@@ -2318,10 +2363,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="C48" t="s">
         <v>280</v>
@@ -2329,10 +2374,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C49" t="s">
         <v>280</v>
@@ -2340,10 +2385,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
         <v>280</v>
@@ -2351,10 +2396,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C51" t="s">
         <v>280</v>
@@ -2362,10 +2407,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
         <v>280</v>
@@ -2373,10 +2418,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
         <v>280</v>
@@ -2384,21 +2429,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C54" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C55" t="s">
         <v>280</v>
@@ -2406,21 +2451,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C56" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B57" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C57" t="s">
         <v>280</v>
@@ -2428,10 +2473,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
         <v>280</v>
@@ -2439,10 +2484,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C59" t="s">
         <v>280</v>
@@ -2450,10 +2495,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s">
         <v>280</v>
@@ -2461,21 +2506,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C61" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
         <v>280</v>
@@ -2483,10 +2528,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C63" t="s">
         <v>280</v>
@@ -2494,21 +2539,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B65" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="C65" t="s">
         <v>280</v>
@@ -2516,10 +2561,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B66" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="C66" t="s">
         <v>280</v>
@@ -2527,10 +2572,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>403</v>
+      </c>
+      <c r="B67" t="s">
         <v>404</v>
-      </c>
-      <c r="B67" t="s">
-        <v>405</v>
       </c>
       <c r="C67" t="s">
         <v>280</v>
@@ -2538,10 +2583,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>405</v>
+      </c>
+      <c r="B68" t="s">
         <v>406</v>
-      </c>
-      <c r="B68" t="s">
-        <v>407</v>
       </c>
       <c r="C68" t="s">
         <v>280</v>
@@ -2549,10 +2594,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>407</v>
+      </c>
+      <c r="B69" t="s">
         <v>408</v>
-      </c>
-      <c r="B69" t="s">
-        <v>409</v>
       </c>
       <c r="C69" t="s">
         <v>280</v>
@@ -2560,10 +2605,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>409</v>
+      </c>
+      <c r="B70" t="s">
         <v>410</v>
-      </c>
-      <c r="B70" t="s">
-        <v>411</v>
       </c>
       <c r="C70" t="s">
         <v>280</v>
@@ -2571,10 +2616,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>411</v>
+      </c>
+      <c r="B71" t="s">
         <v>412</v>
-      </c>
-      <c r="B71" t="s">
-        <v>413</v>
       </c>
       <c r="C71" t="s">
         <v>280</v>
@@ -2582,12 +2627,111 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>413</v>
+      </c>
+      <c r="B72" t="s">
         <v>414</v>
       </c>
-      <c r="B72" t="s">
-        <v>313</v>
-      </c>
       <c r="C72" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" t="s">
+        <v>368</v>
+      </c>
+      <c r="C73" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>416</v>
+      </c>
+      <c r="B74" t="s">
+        <v>309</v>
+      </c>
+      <c r="C74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>417</v>
+      </c>
+      <c r="B75" t="s">
+        <v>418</v>
+      </c>
+      <c r="C75" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>419</v>
+      </c>
+      <c r="B76" t="s">
+        <v>420</v>
+      </c>
+      <c r="C76" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" t="s">
+        <v>422</v>
+      </c>
+      <c r="C77" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>423</v>
+      </c>
+      <c r="B78" t="s">
+        <v>424</v>
+      </c>
+      <c r="C78" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>425</v>
+      </c>
+      <c r="B79" t="s">
+        <v>426</v>
+      </c>
+      <c r="C79" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>427</v>
+      </c>
+      <c r="B80" t="s">
+        <v>317</v>
+      </c>
+      <c r="C80" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>428</v>
+      </c>
+      <c r="B81" t="s">
+        <v>429</v>
+      </c>
+      <c r="C81" t="s">
         <v>280</v>
       </c>
     </row>

--- a/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
@@ -809,7 +809,7 @@
     <t>03_Group_comparisons/Muscle_strength/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>4a470e09e1f60a5ee5de48beaf281dce</t>
+    <t>1ecfd6bd5b85449984cfeaa2a7404e96</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -839,7 +839,7 @@
     <t>02_Groups/Muscle_strength/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>c01dbfe8f31b666a734c29c8bacbd341</t>
+    <t>851e583bf4620ab423e926d384a44233</t>
   </si>
   <si>
     <t>design</t>

--- a/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_strength/F1_Overview/c_data/f1_overview.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2986" uniqueCount="417">
   <si>
     <t>sheet</t>
   </si>
@@ -806,16 +806,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_strength/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>1ecfd6bd5b85449984cfeaa2a7404e96</t>
+    <t>03_Group_comparisons/Muscle_strength/c_data/02_protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>427adf62595b7ecbd86d56ffc78587a6</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_strength/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/c_data/03_set_tests.rds</t>
   </si>
   <si>
     <t>c3c35e87f9ae9f6a9412d96f8c8a33bf</t>
@@ -839,13 +839,13 @@
     <t>02_Groups/Muscle_strength/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>851e583bf4620ab423e926d384a44233</t>
+    <t>6e454a05ef5d8755fdd6468b1c68027c</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_strength/01_Design_Contrasts/c_data/design.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/c_data/01_design.rds</t>
   </si>
   <si>
     <t>c0cfb05785ba25feadb966caf1fa5a50</t>
@@ -956,138 +956,108 @@
     <t>1.2.1</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggh4x</t>
+  </si>
+  <si>
+    <t>0.3.1</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggtext</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
+    <t>CRAN (R 4.6.1)</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gridtext</t>
+  </si>
+  <si>
+    <t>0.1.6</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggh4x</t>
-  </si>
-  <si>
-    <t>0.3.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggtext</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.1)</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gridtext</t>
-  </si>
-  <si>
-    <t>0.1.6</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1124,9 +1094,6 @@
     <t>1.5.0</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1203,12 +1170,6 @@
   </si>
   <si>
     <t>1.3.0</t>
-  </si>
-  <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
   </si>
   <si>
     <t>rprojroot</t>
@@ -1841,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2116,15 +2077,15 @@
         <v>323</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B26" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C26" t="s">
         <v>280</v>
@@ -2138,15 +2099,15 @@
         <v>327</v>
       </c>
       <c r="C27" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>328</v>
+      </c>
+      <c r="B28" t="s">
         <v>329</v>
-      </c>
-      <c r="B28" t="s">
-        <v>319</v>
       </c>
       <c r="C28" t="s">
         <v>280</v>
@@ -2193,7 +2154,7 @@
         <v>337</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2248,7 +2209,7 @@
         <v>347</v>
       </c>
       <c r="C37" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2256,7 +2217,7 @@
         <v>348</v>
       </c>
       <c r="B38" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C38" t="s">
         <v>280</v>
@@ -2264,10 +2225,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C39" t="s">
         <v>280</v>
@@ -2275,10 +2236,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C40" t="s">
         <v>280</v>
@@ -2286,10 +2247,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="C41" t="s">
         <v>280</v>
@@ -2297,32 +2258,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C43" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C44" t="s">
         <v>280</v>
@@ -2330,10 +2291,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
         <v>280</v>
@@ -2341,10 +2302,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C46" t="s">
         <v>280</v>
@@ -2352,10 +2313,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C47" t="s">
         <v>280</v>
@@ -2363,10 +2324,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s">
-        <v>327</v>
+        <v>369</v>
       </c>
       <c r="C48" t="s">
         <v>280</v>
@@ -2374,10 +2335,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C49" t="s">
         <v>280</v>
@@ -2385,10 +2346,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C50" t="s">
         <v>280</v>
@@ -2396,10 +2357,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C51" t="s">
         <v>280</v>
@@ -2407,10 +2368,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C52" t="s">
         <v>280</v>
@@ -2418,10 +2379,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C53" t="s">
         <v>280</v>
@@ -2429,21 +2390,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C54" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B55" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C55" t="s">
         <v>280</v>
@@ -2451,21 +2412,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C57" t="s">
         <v>280</v>
@@ -2473,10 +2434,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C58" t="s">
         <v>280</v>
@@ -2484,10 +2445,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C59" t="s">
         <v>280</v>
@@ -2495,10 +2456,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C60" t="s">
         <v>280</v>
@@ -2506,21 +2467,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C61" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C62" t="s">
         <v>280</v>
@@ -2528,10 +2489,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C63" t="s">
         <v>280</v>
@@ -2539,21 +2500,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B64" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s">
-        <v>400</v>
+        <v>357</v>
       </c>
       <c r="C65" t="s">
         <v>280</v>
@@ -2561,10 +2522,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s">
-        <v>402</v>
+        <v>309</v>
       </c>
       <c r="C66" t="s">
         <v>280</v>
@@ -2572,10 +2533,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C67" t="s">
         <v>280</v>
@@ -2583,10 +2544,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C68" t="s">
         <v>280</v>
@@ -2594,10 +2555,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B69" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C69" t="s">
         <v>280</v>
@@ -2605,10 +2566,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B70" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C70" t="s">
         <v>280</v>
@@ -2616,10 +2577,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B71" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C71" t="s">
         <v>280</v>
@@ -2627,10 +2588,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s">
-        <v>414</v>
+        <v>313</v>
       </c>
       <c r="C72" t="s">
         <v>280</v>
@@ -2641,97 +2602,9 @@
         <v>415</v>
       </c>
       <c r="B73" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
       <c r="C73" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>416</v>
-      </c>
-      <c r="B74" t="s">
-        <v>309</v>
-      </c>
-      <c r="C74" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>417</v>
-      </c>
-      <c r="B75" t="s">
-        <v>418</v>
-      </c>
-      <c r="C75" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>419</v>
-      </c>
-      <c r="B76" t="s">
-        <v>420</v>
-      </c>
-      <c r="C76" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>421</v>
-      </c>
-      <c r="B77" t="s">
-        <v>422</v>
-      </c>
-      <c r="C77" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>423</v>
-      </c>
-      <c r="B78" t="s">
-        <v>424</v>
-      </c>
-      <c r="C78" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>425</v>
-      </c>
-      <c r="B79" t="s">
-        <v>426</v>
-      </c>
-      <c r="C79" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>427</v>
-      </c>
-      <c r="B80" t="s">
-        <v>317</v>
-      </c>
-      <c r="C80" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>428</v>
-      </c>
-      <c r="B81" t="s">
-        <v>429</v>
-      </c>
-      <c r="C81" t="s">
         <v>280</v>
       </c>
     </row>
